--- a/data/trans_orig/AIRE_1_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1_R-Provincia-trans_orig.xlsx
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24907</t>
+          <t>24878</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31932</t>
+          <t>31840</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32389</t>
+          <t>32260</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39926</t>
+          <t>40233</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,67%</t>
+          <t>76,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59850</t>
+          <t>60342</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70451</t>
+          <t>70940</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,93%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,8%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2268</t>
+          <t>2360</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9293</t>
+          <t>9322</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2319</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9856</t>
+          <t>9985</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,33%</t>
+          <t>23,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5994</t>
+          <t>5505</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16595</t>
+          <t>16103</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,07%</t>
         </is>
       </c>
     </row>
@@ -1073,12 +1073,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58702</t>
+          <t>58142</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74852</t>
+          <t>74860</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,92%</t>
+          <t>74,21%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30668</t>
+          <t>31711</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49466</t>
+          <t>49274</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>52,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>80,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>94406</t>
+          <t>95085</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>123687</t>
+          <t>123126</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1158,12 +1158,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,37%</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3496</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>19646</t>
+          <t>20206</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,12 +1221,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11515</t>
+          <t>11707</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30313</t>
+          <t>29270</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1236,12 +1236,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>48,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15642</t>
+          <t>16203</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>44923</t>
+          <t>44244</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>32,24%</t>
+          <t>31,76%</t>
         </is>
       </c>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>15982</t>
+          <t>16365</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23938</t>
+          <t>24536</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1431,12 +1431,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>83,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1451,12 +1451,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21953</t>
+          <t>21667</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28548</t>
+          <t>28471</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>69,85%</t>
+          <t>68,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,84%</t>
+          <t>90,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1486,12 +1486,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40389</t>
+          <t>40642</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51145</t>
+          <t>51447</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,01%</t>
+          <t>84,51%</t>
         </is>
       </c>
     </row>
@@ -1529,12 +1529,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5515</t>
+          <t>4917</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13471</t>
+          <t>13088</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1544,12 +1544,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1564,12 +1564,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2879</t>
+          <t>2956</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9474</t>
+          <t>9760</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1579,12 +1579,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>30,15%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1599,12 +1599,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9735</t>
+          <t>9433</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20491</t>
+          <t>20238</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1614,12 +1614,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>33,24%</t>
         </is>
       </c>
     </row>
@@ -1759,12 +1759,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>17651</t>
+          <t>17680</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26097</t>
+          <t>26456</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>89,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1794,12 +1794,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9935</t>
+          <t>9805</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20573</t>
+          <t>20444</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1809,12 +1809,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>37,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,73%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1829,12 +1829,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30961</t>
+          <t>30919</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45369</t>
+          <t>44645</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1844,12 +1844,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,67%</t>
+          <t>55,6%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>80,28%</t>
         </is>
       </c>
     </row>
@@ -1872,12 +1872,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3386</t>
+          <t>3027</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11832</t>
+          <t>11803</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1887,12 +1887,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,49%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1907,12 +1907,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5558</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16196</t>
+          <t>16326</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1922,12 +1922,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,27%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>61,98%</t>
+          <t>62,48%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10244</t>
+          <t>10968</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24652</t>
+          <t>24694</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,33%</t>
+          <t>44,4%</t>
         </is>
       </c>
     </row>
@@ -2102,12 +2102,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5821</t>
+          <t>5627</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11955</t>
+          <t>12169</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2117,12 +2117,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>50,1%</t>
+          <t>51,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2137,12 +2137,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8931</t>
+          <t>9357</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17003</t>
+          <t>17356</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2152,12 +2152,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>62,22%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2172,12 +2172,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16676</t>
+          <t>16803</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>27133</t>
+          <t>26672</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2187,12 +2187,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,58%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,0%</t>
+          <t>52,1%</t>
         </is>
       </c>
     </row>
@@ -2215,12 +2215,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>11907</t>
+          <t>11693</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18041</t>
+          <t>18235</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2230,12 +2230,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>49,9%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>75,6%</t>
+          <t>76,42%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2250,12 +2250,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>18397</t>
+          <t>17971</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,12 +2265,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>37,78%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2285,12 +2285,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24056</t>
+          <t>24517</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34513</t>
+          <t>34386</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,12 +2300,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,0%</t>
+          <t>47,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,42%</t>
+          <t>67,18%</t>
         </is>
       </c>
     </row>
@@ -2445,12 +2445,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14726</t>
+          <t>14539</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>19717</t>
+          <t>19759</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2460,12 +2460,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19836</t>
+          <t>19356</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28279</t>
+          <t>28152</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2495,12 +2495,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2515,12 +2515,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36396</t>
+          <t>36624</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46243</t>
+          <t>46471</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,64%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>85,83%</t>
         </is>
       </c>
     </row>
@@ -2558,12 +2558,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6098</t>
+          <t>6285</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2573,12 +2573,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2593,12 +2593,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5041</t>
+          <t>5168</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13484</t>
+          <t>13964</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2608,12 +2608,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2628,12 +2628,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7901</t>
+          <t>7673</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17748</t>
+          <t>17520</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2643,12 +2643,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>30511</t>
+          <t>30367</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42984</t>
+          <t>43123</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>53,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,14%</t>
+          <t>76,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35124</t>
+          <t>34556</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51716</t>
+          <t>51921</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,1%</t>
+          <t>43,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>69426</t>
+          <t>70612</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90250</t>
+          <t>90928</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,01%</t>
+          <t>51,88%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,31%</t>
+          <t>66,81%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>13470</t>
+          <t>13331</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>25943</t>
+          <t>26087</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>23,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>46,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27928</t>
+          <t>27723</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>44520</t>
+          <t>45088</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>35,07%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>56,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>45847</t>
+          <t>45169</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>66671</t>
+          <t>65485</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,69%</t>
+          <t>33,19%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>48,12%</t>
         </is>
       </c>
     </row>
@@ -3131,12 +3131,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>45284</t>
+          <t>44712</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>54359</t>
+          <t>54330</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3146,12 +3146,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>76,86%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3166,12 +3166,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>75498</t>
+          <t>76196</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>83163</t>
+          <t>83167</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3181,12 +3181,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3201,12 +3201,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>124185</t>
+          <t>123106</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>135498</t>
+          <t>135287</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3216,12 +3216,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>86,24%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>93,95%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>4560</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>13635</t>
+          <t>14207</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1911</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9576</t>
+          <t>8878</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8496</t>
+          <t>8707</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>19809</t>
+          <t>20888</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>14,51%</t>
         </is>
       </c>
     </row>
@@ -3474,12 +3474,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>237616</t>
+          <t>239906</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>272868</t>
+          <t>273005</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>82,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3509,12 +3509,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>261692</t>
+          <t>262850</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>296993</t>
+          <t>297538</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>67,77%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3544,12 +3544,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>511856</t>
+          <t>510709</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>561089</t>
+          <t>560991</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3559,12 +3559,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>71,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>78,18%</t>
+          <t>78,17%</t>
         </is>
       </c>
     </row>
@@ -3587,12 +3587,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>58675</t>
+          <t>58538</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>93927</t>
+          <t>91637</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3622,12 +3622,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>89156</t>
+          <t>88611</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>124457</t>
+          <t>123299</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3657,12 +3657,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>156602</t>
+          <t>156700</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>205835</t>
+          <t>206982</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3672,12 +3672,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,83%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,84%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/AIRE_1_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/AIRE_1_R-Provincia-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>28614</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>24721</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>31102</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>86,65%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>74,86%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>94,18%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>28963</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>24878</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>31840</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>84,69%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>72,74%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>93,1%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>37084</t>
+          <t>24271</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>32260</t>
+          <t>20226</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40233</t>
+          <t>26622</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>76,36%</t>
+          <t>69,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>66047</t>
+          <t>52885</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>60342</t>
+          <t>47638</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70940</t>
+          <t>56701</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>91,37%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>4409</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>1921</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>8302</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>13,35%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5,82%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>25,14%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5237</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2360</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>9322</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>15,31%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>6,9%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>27,26%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>5161</t>
+          <t>4762</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2411</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9985</t>
+          <t>8807</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>30,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>10398</t>
+          <t>9171</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5505</t>
+          <t>5355</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>16103</t>
+          <t>14418</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>33023</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>33023</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>33023</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>50</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>34200</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>42245</t>
+          <t>29033</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>42245</t>
+          <t>29033</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>42245</t>
+          <t>29033</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>76445</t>
+          <t>62056</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>76445</t>
+          <t>62056</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>76445</t>
+          <t>62056</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67641</t>
+          <t>37950</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58142</t>
+          <t>26951</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74860</t>
+          <t>44184</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>86,33%</t>
+          <t>69,61%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>74,21%</t>
+          <t>49,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>95,55%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>42128</t>
+          <t>41420</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31711</t>
+          <t>36217</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>49274</t>
+          <t>45379</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>69,08%</t>
+          <t>79,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>87,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>109769</t>
+          <t>79370</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>95085</t>
+          <t>67421</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>123126</t>
+          <t>87685</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>74,52%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>68,24%</t>
+          <t>63,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>88,37%</t>
+          <t>82,32%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>16565</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>10331</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>27564</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>30,39%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>18,95%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>50,56%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>10707</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>3488</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>20206</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>13,67%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,45%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>25,79%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>18853</t>
+          <t>10576</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>11707</t>
+          <t>6617</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>29270</t>
+          <t>15779</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>20,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>29560</t>
+          <t>27141</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>16203</t>
+          <t>18826</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>44244</t>
+          <t>39090</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>21,22%</t>
+          <t>25,48%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>17,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>36,7%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>54515</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>54515</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>54515</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>78348</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>78348</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>78348</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>60981</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>60981</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>60981</t>
+          <t>51996</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>139329</t>
+          <t>106511</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>139329</t>
+          <t>106511</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>139329</t>
+          <t>106511</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1406,72 +1406,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>22799</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>19108</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>25303</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>81,65%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>68,43%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>90,62%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>20697</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>16365</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>24536</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>70,27%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>55,56%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>83,3%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25700</t>
+          <t>20669</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21667</t>
+          <t>16414</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>28471</t>
+          <t>24094</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>71,66%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>56,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>46397</t>
+          <t>43469</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>40642</t>
+          <t>37878</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51447</t>
+          <t>47515</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,57%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>66,76%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>83,7%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5124</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2620</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>8815</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>18,35%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>9,38%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>31,57%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>8756</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>4917</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>13088</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>29,73%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>16,7%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>44,44%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>5727</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2956</t>
+          <t>4750</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>9760</t>
+          <t>12430</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>28,34%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>14483</t>
+          <t>13298</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9433</t>
+          <t>9252</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>20238</t>
+          <t>18889</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,27%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27923</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>27923</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>27923</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>49</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>29453</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>29453</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>29453</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31427</t>
+          <t>28844</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>31427</t>
+          <t>28844</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>31427</t>
+          <t>28844</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>60880</t>
+          <t>56767</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>60880</t>
+          <t>56767</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>60880</t>
+          <t>56767</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>15038</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9545</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>20246</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>59,7%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>37,9%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>80,38%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>22558</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>17680</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>26456</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>76,51%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>59,97%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>89,73%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15534</t>
+          <t>22937</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>17261</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>20444</t>
+          <t>27013</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>76,05%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>78,24%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>38092</t>
+          <t>37976</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30919</t>
+          <t>30032</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>44645</t>
+          <t>44507</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>68,49%</t>
+          <t>68,61%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,6%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>80,28%</t>
+          <t>80,41%</t>
         </is>
       </c>
     </row>
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>10150</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4942</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>15643</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>40,3%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>19,62%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>62,1%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>6925</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3027</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>11803</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>23,49%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>10,27%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>40,03%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>10597</t>
+          <t>7222</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5687</t>
+          <t>3146</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16326</t>
+          <t>12898</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>23,95%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>62,48%</t>
+          <t>42,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>17521</t>
+          <t>17371</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10968</t>
+          <t>10840</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>24694</t>
+          <t>25315</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>31,39%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>19,72%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>45,74%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>25188</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>25188</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>25188</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>29483</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>29483</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>29483</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>26131</t>
+          <t>30159</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>26131</t>
+          <t>30159</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26131</t>
+          <t>30159</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>55613</t>
+          <t>55347</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>55613</t>
+          <t>55347</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>55613</t>
+          <t>55347</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>12862</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9231</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>16933</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>46,7%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>33,52%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>61,48%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>8639</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5627</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>12169</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>36,2%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>23,58%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>51,0%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>12979</t>
+          <t>8546</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>9357</t>
+          <t>5784</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17356</t>
+          <t>12329</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>23,76%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,51%</t>
+          <t>50,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>21618</t>
+          <t>21408</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16803</t>
+          <t>16363</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26672</t>
+          <t>26975</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>31,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,1%</t>
+          <t>51,99%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>14681</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>10610</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>18312</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>53,3%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>38,52%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>66,48%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>15223</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>11693</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>18235</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>63,8%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>49,0%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>76,42%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14349</t>
+          <t>15800</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>12017</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>17971</t>
+          <t>18562</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>52,51%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>49,36%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>76,24%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>29571</t>
+          <t>30481</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>24517</t>
+          <t>24914</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>34386</t>
+          <t>35526</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>47,9%</t>
+          <t>48,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>67,18%</t>
+          <t>68,47%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>49</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>27543</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>27543</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>27543</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>48</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>23862</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>23862</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>23862</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>49</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27328</t>
+          <t>24346</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>27328</t>
+          <t>24346</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>27328</t>
+          <t>24346</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>51189</t>
+          <t>51889</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>51189</t>
+          <t>51889</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>51189</t>
+          <t>51889</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2435,72 +2435,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>21269</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>16752</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>24443</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>72,91%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>57,43%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>83,79%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>17908</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>14539</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>19759</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>86,0%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>69,82%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>94,89%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>24184</t>
+          <t>17784</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19356</t>
+          <t>14846</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>28152</t>
+          <t>19655</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>42092</t>
+          <t>39053</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36624</t>
+          <t>34503</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46471</t>
+          <t>43036</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>67,64%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>86,38%</t>
         </is>
       </c>
     </row>
@@ -2548,72 +2548,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>7901</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>4727</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>12418</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>27,09%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>16,21%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>42,57%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>2916</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>6285</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>14,0%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>5,11%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>30,18%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>9136</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13964</t>
+          <t>5809</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>12052</t>
+          <t>10772</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7673</t>
+          <t>6789</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17520</t>
+          <t>15322</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>30,75%</t>
         </is>
       </c>
     </row>
@@ -2661,57 +2661,57 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>29170</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>29170</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>29170</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>20824</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>20824</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>20824</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>33320</t>
+          <t>20655</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>33320</t>
+          <t>20655</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>33320</t>
+          <t>20655</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>54144</t>
+          <t>49825</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>54144</t>
+          <t>49825</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>54144</t>
+          <t>49825</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>40812</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>33267</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>48022</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>54,72%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>44,61%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>64,39%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>36910</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>30367</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>43123</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>65,38%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>53,79%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>76,39%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>43660</t>
+          <t>34556</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34556</t>
+          <t>27954</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>51921</t>
+          <t>40639</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>62,72%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>43,39%</t>
+          <t>50,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>80569</t>
+          <t>75369</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>70612</t>
+          <t>64762</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>90928</t>
+          <t>84429</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>59,2%</t>
+          <t>58,12%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>51,88%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,81%</t>
+          <t>65,11%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>33765</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>26555</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>41310</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>45,28%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>35,61%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>55,39%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>19544</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>13331</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>26087</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>34,62%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>23,61%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>46,21%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>35984</t>
+          <t>20536</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>27723</t>
+          <t>14453</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>45088</t>
+          <t>27138</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>37,28%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,61%</t>
+          <t>49,26%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>55528</t>
+          <t>54301</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>45169</t>
+          <t>45241</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>65485</t>
+          <t>64908</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>40,8%</t>
+          <t>41,88%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>33,19%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>48,12%</t>
+          <t>50,06%</t>
         </is>
       </c>
     </row>
@@ -3004,57 +3004,57 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>74577</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>74577</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>74577</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>80</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>56454</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>56454</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>56454</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>79644</t>
+          <t>55092</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>79644</t>
+          <t>55092</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>79644</t>
+          <t>55092</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>136097</t>
+          <t>129670</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>136097</t>
+          <t>129670</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>136097</t>
+          <t>129670</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3121,72 +3121,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>81394</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>76480</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>84142</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>94,62%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>88,9%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>97,81%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>81</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>50358</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>44712</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>54330</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>85,47%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>75,89%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>92,21%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>80420</t>
+          <t>51513</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>76196</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>83167</t>
+          <t>55698</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>75,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>130779</t>
+          <t>132907</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>123106</t>
+          <t>125961</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>135287</t>
+          <t>138274</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,88%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,28%</t>
         </is>
       </c>
     </row>
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>4631</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>1883</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>9545</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>5,38%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>11,1%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>8561</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>4589</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>14207</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>14,53%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>7,79%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>24,11%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>4654</t>
+          <t>9131</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>4946</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>8878</t>
+          <t>14844</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>13215</t>
+          <t>13762</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>8707</t>
+          <t>8395</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>20888</t>
+          <t>20708</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,12%</t>
         </is>
       </c>
     </row>
@@ -3347,57 +3347,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>86025</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>86025</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>86025</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>92</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>58919</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>58919</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>58919</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>85074</t>
+          <t>60644</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>85074</t>
+          <t>60644</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>85074</t>
+          <t>60644</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>143994</t>
+          <t>146669</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>143994</t>
+          <t>146669</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>143994</t>
+          <t>146669</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3464,72 +3464,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>372</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>260739</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>244156</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>275967</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>72,84%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>68,21%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>77,09%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>346</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>253675</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>239906</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>273005</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>76,51%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>72,36%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>82,34%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>281689</t>
+          <t>221696</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>262850</t>
+          <t>208646</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>297538</t>
+          <t>233782</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>77,05%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>535363</t>
+          <t>482435</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>510709</t>
+          <t>461960</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>560991</t>
+          <t>501963</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>76,2%</t>
         </is>
       </c>
     </row>
@@ -3577,72 +3577,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>97226</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>81998</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>113809</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>27,16%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>22,91%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>31,79%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>122</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>77868</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>58538</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>91637</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>23,49%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>17,66%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>27,64%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>104460</t>
+          <t>79073</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>88611</t>
+          <t>66987</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>123299</t>
+          <t>92123</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>22,95%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>182328</t>
+          <t>176298</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>156700</t>
+          <t>156770</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>206982</t>
+          <t>196773</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>23,8%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>28,84%</t>
+          <t>29,87%</t>
         </is>
       </c>
     </row>
@@ -3690,57 +3690,57 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>511</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>357965</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>468</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>331543</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>511</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>386149</t>
+          <t>300769</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>386149</t>
+          <t>300769</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>386149</t>
+          <t>300769</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>717691</t>
+          <t>658733</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
